--- a/base de datos .xlsx
+++ b/base de datos .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicholaspalmacarvajal/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11E29C92-9161-9D4F-9D4A-09E116A7F03F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B317B475-FE42-6C4A-97F5-6DA62AD5CB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5580" yWindow="2300" windowWidth="27640" windowHeight="16940" xr2:uid="{C0D352D5-618F-DB4C-9FE9-D986D600BC72}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="103">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -49,24 +49,9 @@
     <t>Av. José Miguel Infante 8745, Renca, Región Metropolitana</t>
   </si>
   <si>
-    <t>HOSPITAL MUTUAL DE SEGURIDAD</t>
-  </si>
-  <si>
-    <t>Av. Libertador Bernardo O'Higgins 4848, 9190015 Libertador Bernardo O Higgins, Estación Central, Región Metropolitana</t>
-  </si>
-  <si>
-    <t>TUCAPEL CD</t>
-  </si>
-  <si>
     <t>VOLCAN LINCABUR 435, PUDAHUEL</t>
   </si>
   <si>
-    <t>ECONUT PARCELA 30</t>
-  </si>
-  <si>
-    <t>18 SEPT, Paine</t>
-  </si>
-  <si>
     <t>CV TRADING</t>
   </si>
   <si>
@@ -79,18 +64,6 @@
     <t>La Estancilla 8991, Buin, Región Metropolitana</t>
   </si>
   <si>
-    <t>LA PINTANA</t>
-  </si>
-  <si>
-    <t>Lautaro 2260, La Pintana</t>
-  </si>
-  <si>
-    <t>PUENTE VERDE</t>
-  </si>
-  <si>
-    <t>Avenida Puente Verde 2080, Quilicura</t>
-  </si>
-  <si>
     <t>FINE FRUITS</t>
   </si>
   <si>
@@ -127,36 +100,18 @@
     <t>RAMON SUBERCASEUX 2712, Pirque, Chile</t>
   </si>
   <si>
-    <t>WALMART</t>
-  </si>
-  <si>
     <t>Av. El Parque 1000, Pudahuel, Región Metropolitana</t>
   </si>
   <si>
-    <t>LIDER BUIN</t>
-  </si>
-  <si>
-    <t>San Martín 555, buin</t>
-  </si>
-  <si>
     <t>LA INVERNADA</t>
   </si>
   <si>
     <t>CAMINO SAN MIGUEL PARC 2 PAINE</t>
   </si>
   <si>
-    <t>PLANTA DAFF (HEREDIA)</t>
-  </si>
-  <si>
-    <t>PANAMERICANA NORTE 16950 LAMPA</t>
-  </si>
-  <si>
     <t>AGROCOMMERCE LOGINSA</t>
   </si>
   <si>
-    <t>LO SIERRA 04460 SAN BDO</t>
-  </si>
-  <si>
     <t>PACKING MERQUEN</t>
   </si>
   <si>
@@ -205,12 +160,6 @@
     <t>CAMINO LAS PARCELAS 21 ISLA DE MAIPO</t>
   </si>
   <si>
-    <t>BALMACEDA</t>
-  </si>
-  <si>
-    <t>BALMACEDA 1726 STGO</t>
-  </si>
-  <si>
     <t>GOOD FOOD</t>
   </si>
   <si>
@@ -226,54 +175,6 @@
     <t>FUNDO CHALLAY ALTO, HUELQUEN, PAINE</t>
   </si>
   <si>
-    <t>DEGESCH</t>
-  </si>
-  <si>
-    <t>JOSE LUIS CARO 1321, PADRE HURTADO</t>
-  </si>
-  <si>
-    <t>CAROZZI NOS</t>
-  </si>
-  <si>
-    <t>LONGITUDINAL SUR 5201, NOS</t>
-  </si>
-  <si>
-    <t>MSC MAIPU</t>
-  </si>
-  <si>
-    <t>AV. PAJARITOS 1061 MAIPU</t>
-  </si>
-  <si>
-    <t>MOLINO EXPOSICION</t>
-  </si>
-  <si>
-    <t>AV. EXPOSICION 1657 EST CENTRAL</t>
-  </si>
-  <si>
-    <t>MOLINO BALMACEDA</t>
-  </si>
-  <si>
-    <t>MSC EXPOSICION</t>
-  </si>
-  <si>
-    <t>ECONUT PLANTA</t>
-  </si>
-  <si>
-    <t>18 SEPT, PAINE</t>
-  </si>
-  <si>
-    <t>ECONUT</t>
-  </si>
-  <si>
-    <t>TUCAPEL PRODUCCION</t>
-  </si>
-  <si>
-    <t>TALLER GAMMA</t>
-  </si>
-  <si>
-    <t>Mapocho  # 4573 , Quinta Normal.</t>
-  </si>
-  <si>
     <t>LO SIERRA 4466 SAN BDO.</t>
   </si>
   <si>
@@ -281,13 +182,175 @@
   </si>
   <si>
     <t>CAMINO EL OLIVETO 4193 TALAGANTE</t>
+  </si>
+  <si>
+    <t>SUCURSAL</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUCAPEL </t>
+  </si>
+  <si>
+    <t>RUT</t>
+  </si>
+  <si>
+    <t>91.083.000-7</t>
+  </si>
+  <si>
+    <t>76.730.550-8</t>
+  </si>
+  <si>
+    <t>78.254.990-1</t>
+  </si>
+  <si>
+    <t>96.973.910-0</t>
+  </si>
+  <si>
+    <t>76.198.770-4</t>
+  </si>
+  <si>
+    <t>76.746.693-5</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA MOLINERA SAN CRISTOBAL S.A. (CASABLANCA)</t>
+  </si>
+  <si>
+    <t>Alejandro Galaz N° 500, Casablanca</t>
+  </si>
+  <si>
+    <t>MOLINO LA ESTAMPA S.A.</t>
+  </si>
+  <si>
+    <t>Fermin Vivaceta 1053, Independencia</t>
+  </si>
+  <si>
+    <t>MOLINO FERRER HERMANOS S.A.</t>
+  </si>
+  <si>
+    <t>Baquedano N° 647, San Bernardo</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA MOLINERA SAN CRISTOBAL S.A. (EXPOSICIÓN)</t>
+  </si>
+  <si>
+    <t>Exposición N° 1657, Estación Central</t>
+  </si>
+  <si>
+    <t>MOLINO LINDEROS S.A.</t>
+  </si>
+  <si>
+    <t>Villaseca Nº 1195, Buin</t>
+  </si>
+  <si>
+    <t>COMPAÑÍA MOLINERA SAN CRISTOBAL S.A. (MAIPÚ)</t>
+  </si>
+  <si>
+    <t>Avenida Pajarito N° 1046, Maipú</t>
+  </si>
+  <si>
+    <t>EMPRESAS CAROZZI S.A</t>
+  </si>
+  <si>
+    <t>Longitudinal sur Km 21, San Bernardo.</t>
+  </si>
+  <si>
+    <t>Ruta 5 sur Km 53, N°19200 Paine</t>
+  </si>
+  <si>
+    <t>90.060.000-3</t>
+  </si>
+  <si>
+    <t>ANGOSTURA FOODS</t>
+  </si>
+  <si>
+    <t>78.346.122-6</t>
+  </si>
+  <si>
+    <t>76.591.040-9</t>
+  </si>
+  <si>
+    <t>92.156.000-1</t>
+  </si>
+  <si>
+    <t>91.617.000-7</t>
+  </si>
+  <si>
+    <t>90.828.005-8</t>
+  </si>
+  <si>
+    <t>78.788.100-9</t>
+  </si>
+  <si>
+    <t>96.924.340-7</t>
+  </si>
+  <si>
+    <t>MOLINERA SAN CRISTOBAL - MALLOCO</t>
+  </si>
+  <si>
+    <t>Manuel Gonzalez N° 514, Peñaflor</t>
+  </si>
+  <si>
+    <t>76.399.776-6</t>
+  </si>
+  <si>
+    <t>81.852.700-4</t>
+  </si>
+  <si>
+    <t>76.360.868-9</t>
+  </si>
+  <si>
+    <t>76.665.460-0</t>
+  </si>
+  <si>
+    <t>76.410.833-7</t>
+  </si>
+  <si>
+    <t>76.185.455-0</t>
+  </si>
+  <si>
+    <t>76.948.219-9</t>
+  </si>
+  <si>
+    <t>91.845.000-7</t>
+  </si>
+  <si>
+    <t>76.572.070.7</t>
+  </si>
+  <si>
+    <t>77.015.053-1</t>
+  </si>
+  <si>
+    <t>76.263.274-7</t>
+  </si>
+  <si>
+    <t>WALMART Quilicura</t>
+  </si>
+  <si>
+    <t>WALMART Pudahuel</t>
+  </si>
+  <si>
+    <t>76.042.014-k</t>
+  </si>
+  <si>
+    <t>Ojos del salado N°0781, Quilicura</t>
+  </si>
+  <si>
+    <t>96.689.090-7</t>
+  </si>
+  <si>
+    <t>91.942.000-6</t>
+  </si>
+  <si>
+    <t>78.279.920-7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -308,6 +371,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -330,10 +405,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -648,387 +725,516 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E34372F9-71FE-6F40-9DE2-78229A10F9DD}">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.5" customWidth="1"/>
+    <col min="1" max="1" width="46.33203125" customWidth="1"/>
     <col min="2" max="2" width="96.1640625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+      <c r="C21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
+      <c r="C27" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B28" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
+      <c r="C28" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B29" s="4" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
+      <c r="C29" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B30" s="4" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
+      <c r="C30" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B31" s="4" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
+      <c r="C31" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B32" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
+      <c r="C32" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B33" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
+      <c r="C33" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
+      <c r="B34" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="2" t="s">
+      <c r="C34" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C35" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/base de datos .xlsx
+++ b/base de datos .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicholaspalmacarvajal/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B317B475-FE42-6C4A-97F5-6DA62AD5CB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417A4E1B-AA05-C540-93AF-7F61E4B5ACE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5580" yWindow="2300" windowWidth="27640" windowHeight="16940" xr2:uid="{C0D352D5-618F-DB4C-9FE9-D986D600BC72}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="107">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -344,6 +344,18 @@
   </si>
   <si>
     <t>78.279.920-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPEFRUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">av curico 3320 , curico </t>
+  </si>
+  <si>
+    <t>CURICO</t>
+  </si>
+  <si>
+    <t>9.866.957-4</t>
   </si>
 </sst>
 </file>
@@ -725,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E34372F9-71FE-6F40-9DE2-78229A10F9DD}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="46.33203125" customWidth="1"/>
@@ -1237,6 +1249,20 @@
         <v>74</v>
       </c>
     </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/base de datos .xlsx
+++ b/base de datos .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicholaspalmacarvajal/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417A4E1B-AA05-C540-93AF-7F61E4B5ACE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECDE4C0-19AF-784D-819F-7FF2B30A3CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5580" yWindow="2300" windowWidth="27640" windowHeight="16940" xr2:uid="{C0D352D5-618F-DB4C-9FE9-D986D600BC72}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="110">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -346,16 +346,25 @@
     <t>78.279.920-7</t>
   </si>
   <si>
-    <t xml:space="preserve">COPEFRUT </t>
-  </si>
-  <si>
-    <t xml:space="preserve">av curico 3320 , curico </t>
-  </si>
-  <si>
     <t>CURICO</t>
   </si>
   <si>
-    <t>9.866.957-4</t>
+    <t>76.140.787-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El almendro lote 6B-7 S/N Pencahue </t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMERCIALIZADORA  RIO CLARO DEL MAULE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSA INTERNATIONAL SPA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camino lo Hermogenes km 07 Requinoa </t>
+  </si>
+  <si>
+    <t>77.474.814-8</t>
   </si>
 </sst>
 </file>
@@ -737,7 +746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E34372F9-71FE-6F40-9DE2-78229A10F9DD}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="46.33203125" customWidth="1"/>
@@ -1251,16 +1260,30 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="D37" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>106</v>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/base de datos .xlsx
+++ b/base de datos .xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicholaspalmacarvajal/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicholaspalmacarvajal/Desktop/Rentokil-Initial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECDE4C0-19AF-784D-819F-7FF2B30A3CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CFB6593-28B4-004A-A7F4-BFEEAE9C2EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5580" yWindow="2300" windowWidth="27640" windowHeight="16940" xr2:uid="{C0D352D5-618F-DB4C-9FE9-D986D600BC72}"/>
   </bookViews>
@@ -214,9 +214,6 @@
     <t>76.746.693-5</t>
   </si>
   <si>
-    <t>COMPAÑÍA MOLINERA SAN CRISTOBAL S.A. (CASABLANCA)</t>
-  </si>
-  <si>
     <t>Alejandro Galaz N° 500, Casablanca</t>
   </si>
   <si>
@@ -232,9 +229,6 @@
     <t>Baquedano N° 647, San Bernardo</t>
   </si>
   <si>
-    <t>COMPAÑÍA MOLINERA SAN CRISTOBAL S.A. (EXPOSICIÓN)</t>
-  </si>
-  <si>
     <t>Exposición N° 1657, Estación Central</t>
   </si>
   <si>
@@ -244,9 +238,6 @@
     <t>Villaseca Nº 1195, Buin</t>
   </si>
   <si>
-    <t>COMPAÑÍA MOLINERA SAN CRISTOBAL S.A. (MAIPÚ)</t>
-  </si>
-  <si>
     <t>Avenida Pajarito N° 1046, Maipú</t>
   </si>
   <si>
@@ -365,6 +356,15 @@
   </si>
   <si>
     <t>77.474.814-8</t>
+  </si>
+  <si>
+    <t>CIA  MOLINERA SAN CRISTOBAL S.A. CASABLANCA</t>
+  </si>
+  <si>
+    <t>CIA  MOLINERA SAN CRISTOBAL S.A. EXPOSICIÓN</t>
+  </si>
+  <si>
+    <t>CIA  MOLINERA SAN CRISTOBAL S.A.MAIPÚ</t>
   </si>
 </sst>
 </file>
@@ -835,7 +835,7 @@
         <v>50</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -863,7 +863,7 @@
         <v>50</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -877,7 +877,7 @@
         <v>50</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -891,26 +891,26 @@
         <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="C11" t="s">
         <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>21</v>
@@ -919,7 +919,7 @@
         <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -933,7 +933,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -947,7 +947,7 @@
         <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -961,7 +961,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -1003,7 +1003,7 @@
         <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -1017,7 +1017,7 @@
         <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -1031,7 +1031,7 @@
         <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -1045,7 +1045,7 @@
         <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -1059,7 +1059,7 @@
         <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -1073,7 +1073,7 @@
         <v>50</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -1087,7 +1087,7 @@
         <v>50</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -1101,7 +1101,7 @@
         <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -1129,161 +1129,161 @@
         <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>60</v>
-      </c>
       <c r="C28" s="4" t="s">
         <v>50</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="C29" s="4" t="s">
         <v>50</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>64</v>
-      </c>
       <c r="C30" s="4" t="s">
         <v>50</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>50</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>50</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>50</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>50</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>50</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/base de datos .xlsx
+++ b/base de datos .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicholaspalmacarvajal/Desktop/Rentokil-Initial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CFB6593-28B4-004A-A7F4-BFEEAE9C2EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8FB34E-0283-2C42-9ABD-89CF9CA51FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5580" yWindow="2300" windowWidth="27640" windowHeight="16940" xr2:uid="{C0D352D5-618F-DB4C-9FE9-D986D600BC72}"/>
   </bookViews>
@@ -361,10 +361,10 @@
     <t>CIA  MOLINERA SAN CRISTOBAL S.A. CASABLANCA</t>
   </si>
   <si>
-    <t>CIA  MOLINERA SAN CRISTOBAL S.A. EXPOSICIÓN</t>
-  </si>
-  <si>
-    <t>CIA  MOLINERA SAN CRISTOBAL S.A.MAIPÚ</t>
+    <t>CIA  MOLINERA SAN CRISTOBAL S.A.MAIPU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIA  MOLINERA SAN CRISTOBAL S.A. EXPOSICION </t>
   </si>
 </sst>
 </file>
@@ -1176,7 +1176,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>64</v>
@@ -1204,7 +1204,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>67</v>

--- a/base de datos .xlsx
+++ b/base de datos .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicholaspalmacarvajal/Desktop/Rentokil-Initial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8FB34E-0283-2C42-9ABD-89CF9CA51FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9E6EDE-7B8E-6943-BD33-D3BD9D867007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5580" yWindow="2300" windowWidth="27640" windowHeight="16940" xr2:uid="{C0D352D5-618F-DB4C-9FE9-D986D600BC72}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="113">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -365,6 +365,15 @@
   </si>
   <si>
     <t xml:space="preserve">CIA  MOLINERA SAN CRISTOBAL S.A. EXPOSICION </t>
+  </si>
+  <si>
+    <t>Avenida Charles AranguizSandoval 467 -Puente Alto/ RM</t>
+  </si>
+  <si>
+    <t>77.603.820-2</t>
+  </si>
+  <si>
+    <t>Encipharm SPA</t>
   </si>
 </sst>
 </file>
@@ -746,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E34372F9-71FE-6F40-9DE2-78229A10F9DD}">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="46.33203125" customWidth="1"/>
@@ -1286,6 +1295,20 @@
         <v>106</v>
       </c>
     </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>112</v>
+      </c>
+      <c r="B39" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39" t="s">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
